--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>281298.01</v>
+        <v>353529</v>
       </c>
       <c r="E3" t="n">
         <v>273584.33</v>
@@ -580,7 +580,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>281298.01</v>
+        <v>353529</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6002186.96</v>
+        <v>6030471.4</v>
       </c>
       <c r="E4" t="n">
         <v>6000116.51</v>
@@ -617,7 +617,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>6002186.96</v>
+        <v>6030471.4</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331082087.64</v>
+        <v>376274941.96</v>
       </c>
       <c r="E7" t="n">
-        <v>172353813.93</v>
+        <v>174841374.21</v>
       </c>
       <c r="F7" t="n">
-        <v>159501385.8</v>
+        <v>165533877.71</v>
       </c>
       <c r="G7" t="n">
         <v>17505440.57</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320456370.03</v>
+        <v>365649224.35</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -770,7 +770,7 @@
         <v>22345704.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>181847090.52</v>
+        <v>187879582.43</v>
       </c>
     </row>
     <row r="8">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50432.87</v>
+        <v>63156.57</v>
       </c>
       <c r="E8" t="n">
         <v>50432.87</v>
@@ -801,7 +801,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>50432.87</v>
+        <v>63156.57</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -881,10 +881,10 @@
         <v>287221.89</v>
       </c>
       <c r="E10" t="n">
-        <v>123303.87</v>
+        <v>126290.67</v>
       </c>
       <c r="F10" t="n">
-        <v>34115.73</v>
+        <v>34200.17</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -899,7 +899,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>34115.73</v>
+        <v>34200.17</v>
       </c>
     </row>
     <row r="11">
@@ -918,10 +918,10 @@
         <v>364747.57</v>
       </c>
       <c r="E11" t="n">
-        <v>272051.45</v>
+        <v>304401.1</v>
       </c>
       <c r="F11" t="n">
-        <v>230151.2</v>
+        <v>257526.78</v>
       </c>
       <c r="G11" t="n">
         <v>31325.06</v>
@@ -954,7 +954,7 @@
         <v>26472.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>256624.1</v>
+        <v>283999.68</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>462446.22</v>
+        <v>513818.81</v>
       </c>
       <c r="E13" t="n">
         <v>373331.96</v>
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>462446.22</v>
+        <v>513818.81</v>
       </c>
       <c r="N13" t="n">
         <v>1339.42</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4975571.29</v>
+        <v>4975358.49</v>
       </c>
       <c r="E14" t="n">
-        <v>3149717.88</v>
+        <v>3651533.41</v>
       </c>
       <c r="F14" t="n">
-        <v>2604473.41</v>
+        <v>2685509.95</v>
       </c>
       <c r="G14" t="n">
         <v>302674.08</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>4249533.32</v>
+        <v>4249320.52</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>
@@ -1119,7 +1119,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2873093.47</v>
+        <v>2954130.01</v>
       </c>
     </row>
     <row r="15">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>473642.26</v>
+        <v>524988.46</v>
       </c>
       <c r="E15" t="n">
         <v>386219.63</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>473642.26</v>
+        <v>524988.46</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>9027832.08</v>
       </c>
       <c r="F16" t="n">
-        <v>6541502.76</v>
+        <v>7624144.79</v>
       </c>
       <c r="G16" t="n">
         <v>565340.29</v>
@@ -1229,7 +1229,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>7018443.02</v>
+        <v>8101085.05</v>
       </c>
     </row>
     <row r="17">
@@ -1358,10 +1358,10 @@
         <v>14891992.87</v>
       </c>
       <c r="E19" t="n">
-        <v>3736274.77</v>
+        <v>3967655.98</v>
       </c>
       <c r="F19" t="n">
-        <v>3733169.77</v>
+        <v>3790571.98</v>
       </c>
       <c r="G19" t="n">
         <v>2101197.2</v>
@@ -1394,7 +1394,7 @@
         <v>2071339.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>5804509.73</v>
+        <v>5861911.94</v>
       </c>
     </row>
     <row r="20">
@@ -1468,10 +1468,10 @@
         <v>8604166.130000001</v>
       </c>
       <c r="E21" t="n">
-        <v>8494480.630000001</v>
+        <v>8529258.880000001</v>
       </c>
       <c r="F21" t="n">
-        <v>8494842.630000001</v>
+        <v>8529620.880000001</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>8494842.630000001</v>
+        <v>8529620.880000001</v>
       </c>
     </row>
     <row r="22">
